--- a/public/data/content.xlsx
+++ b/public/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nerii\Desktop\Work\misc\S-SE\Kosovo Pavillon\_deployments\venicebiennial25-kosovo\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7432AB-E4E4-4E83-A587-085A6766D56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FB17E4-01B5-409E-A96C-9E2A566241B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="162">
   <si>
     <t>folder</t>
   </si>
@@ -495,9 +495,6 @@
   </si>
   <si>
     <t>other narrative</t>
-  </si>
-  <si>
-    <t>png</t>
   </si>
   <si>
     <t>DSC5056</t>
@@ -1124,7 +1121,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>25</v>
@@ -1160,7 +1157,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>29</v>
@@ -1196,7 +1193,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>31</v>
@@ -1232,7 +1229,7 @@
         <v>32</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>33</v>
@@ -1268,7 +1265,7 @@
         <v>35</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>36</v>
@@ -1304,7 +1301,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>38</v>
@@ -1340,7 +1337,7 @@
         <v>39</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>40</v>
@@ -1376,7 +1373,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>43</v>
@@ -1412,7 +1409,7 @@
         <v>44</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>45</v>
@@ -1448,7 +1445,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>48</v>
@@ -1484,7 +1481,7 @@
         <v>49</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>50</v>
@@ -1520,7 +1517,7 @@
         <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>52</v>
@@ -1556,7 +1553,7 @@
         <v>54</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>55</v>
@@ -1592,7 +1589,7 @@
         <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>57</v>
@@ -1628,7 +1625,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>59</v>
@@ -1664,7 +1661,7 @@
         <v>61</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>62</v>
@@ -3569,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>64</v>
@@ -3603,7 +3600,7 @@
         <v>14</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>64</v>
@@ -3637,7 +3634,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>64</v>
@@ -3671,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>64</v>
